--- a/CLASSWORK DAY 2.xlsx
+++ b/CLASSWORK DAY 2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\excel_works\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3C31DE06-AF94-4353-92C5-01931AA0E1C5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0C1DBE1-D481-4B07-AD0B-26639877EFE9}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="14380" windowHeight="4070" xr2:uid="{24ED689C-E62B-47DC-9E5F-1B1154BF4233}"/>
   </bookViews>
